--- a/data/cards.xlsx
+++ b/data/cards.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:S33"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,6 +436,27 @@
       <c r="L1" t="str">
         <v>description</v>
       </c>
+      <c r="M1" t="str">
+        <v>dribble</v>
+      </c>
+      <c r="N1" t="str">
+        <v>passing</v>
+      </c>
+      <c r="O1" t="str">
+        <v>shooting</v>
+      </c>
+      <c r="P1" t="str">
+        <v>tackling</v>
+      </c>
+      <c r="Q1" t="str">
+        <v>intercept</v>
+      </c>
+      <c r="R1" t="str">
+        <v>blocking</v>
+      </c>
+      <c r="S1" t="str">
+        <v>goalkeeping</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -472,7 +493,28 @@
         <v>card_gk_001</v>
       </c>
       <c r="L2" t="str">
-        <v>稳健守门员</v>
+        <v>少林守门僧，铜皮铁骨守龙门</v>
+      </c>
+      <c r="M2">
+        <v>20</v>
+      </c>
+      <c r="N2">
+        <v>30</v>
+      </c>
+      <c r="O2">
+        <v>10</v>
+      </c>
+      <c r="P2">
+        <v>30</v>
+      </c>
+      <c r="Q2">
+        <v>25</v>
+      </c>
+      <c r="R2">
+        <v>65</v>
+      </c>
+      <c r="S2">
+        <v>85</v>
       </c>
     </row>
     <row r="3">
@@ -504,13 +546,34 @@
         <v>skill_tackle</v>
       </c>
       <c r="J3" t="str">
-        <v/>
+        <v>skill_iron_wall</v>
       </c>
       <c r="K3" t="str">
         <v>card_df_001</v>
       </c>
       <c r="L3" t="str">
-        <v>坚固后卫</v>
+        <v>铁布衫传人，防守固若金汤</v>
+      </c>
+      <c r="M3">
+        <v>35</v>
+      </c>
+      <c r="N3">
+        <v>40</v>
+      </c>
+      <c r="O3">
+        <v>30</v>
+      </c>
+      <c r="P3">
+        <v>80</v>
+      </c>
+      <c r="Q3">
+        <v>75</v>
+      </c>
+      <c r="R3">
+        <v>78</v>
+      </c>
+      <c r="S3">
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -530,10 +593,10 @@
         <v>30</v>
       </c>
       <c r="F4">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="G4">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="H4">
         <v>45</v>
@@ -548,7 +611,28 @@
         <v>card_df_002</v>
       </c>
       <c r="L4" t="str">
-        <v>快速后卫</v>
+        <v>金钟罩弟子，速度型后卫</v>
+      </c>
+      <c r="M4">
+        <v>40</v>
+      </c>
+      <c r="N4">
+        <v>45</v>
+      </c>
+      <c r="O4">
+        <v>28</v>
+      </c>
+      <c r="P4">
+        <v>70</v>
+      </c>
+      <c r="Q4">
+        <v>68</v>
+      </c>
+      <c r="R4">
+        <v>62</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -586,7 +670,28 @@
         <v>card_mf_001</v>
       </c>
       <c r="L5" t="str">
-        <v>全能中场</v>
+        <v>太极拳新秀，攻守兼备</v>
+      </c>
+      <c r="M5">
+        <v>65</v>
+      </c>
+      <c r="N5">
+        <v>72</v>
+      </c>
+      <c r="O5">
+        <v>55</v>
+      </c>
+      <c r="P5">
+        <v>58</v>
+      </c>
+      <c r="Q5">
+        <v>55</v>
+      </c>
+      <c r="R5">
+        <v>40</v>
+      </c>
+      <c r="S5">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -594,37 +699,58 @@
         <v>mf_002</v>
       </c>
       <c r="B6" t="str">
-        <v>刘组织</v>
+        <v>林快腿</v>
       </c>
       <c r="C6" t="str">
         <v>MID</v>
       </c>
       <c r="D6">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E6">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="F6">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="G6">
-        <v>65</v>
+        <v>78</v>
       </c>
       <c r="H6">
-        <v>85</v>
+        <v>62</v>
       </c>
       <c r="I6" t="str">
-        <v>skill_through</v>
+        <v>skill_dribble</v>
       </c>
       <c r="J6" t="str">
-        <v>skill_freekick</v>
+        <v/>
       </c>
       <c r="K6" t="str">
         <v>card_mf_002</v>
       </c>
       <c r="L6" t="str">
-        <v>组织核心</v>
+        <v>迷踪步小子，速度见长</v>
+      </c>
+      <c r="M6">
+        <v>70</v>
+      </c>
+      <c r="N6">
+        <v>58</v>
+      </c>
+      <c r="O6">
+        <v>48</v>
+      </c>
+      <c r="P6">
+        <v>48</v>
+      </c>
+      <c r="Q6">
+        <v>45</v>
+      </c>
+      <c r="R6">
+        <v>32</v>
+      </c>
+      <c r="S6">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -638,31 +764,52 @@
         <v>FWD</v>
       </c>
       <c r="D7">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E7">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="F7">
         <v>25</v>
       </c>
       <c r="G7">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="H7">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="I7" t="str">
         <v>skill_shot</v>
       </c>
       <c r="J7" t="str">
-        <v>skill_dribble</v>
+        <v/>
       </c>
       <c r="K7" t="str">
         <v>card_fw_001</v>
       </c>
       <c r="L7" t="str">
-        <v>锋线杀手</v>
+        <v>佛山无影脚，射门精准</v>
+      </c>
+      <c r="M7">
+        <v>72</v>
+      </c>
+      <c r="N7">
+        <v>55</v>
+      </c>
+      <c r="O7">
+        <v>78</v>
+      </c>
+      <c r="P7">
+        <v>25</v>
+      </c>
+      <c r="Q7">
+        <v>20</v>
+      </c>
+      <c r="R7">
+        <v>18</v>
+      </c>
+      <c r="S7">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -676,19 +823,19 @@
         <v>FWD</v>
       </c>
       <c r="D8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E8">
-        <v>75</v>
+        <v>62</v>
       </c>
       <c r="F8">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="G8">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="H8">
-        <v>70</v>
+        <v>58</v>
       </c>
       <c r="I8" t="str">
         <v>skill_dribble</v>
@@ -700,50 +847,1508 @@
         <v>card_fw_002</v>
       </c>
       <c r="L8" t="str">
-        <v>极速边锋</v>
+        <v>燕青拳新星，极速边路</v>
+      </c>
+      <c r="M8">
+        <v>78</v>
+      </c>
+      <c r="N8">
+        <v>50</v>
+      </c>
+      <c r="O8">
+        <v>62</v>
+      </c>
+      <c r="P8">
+        <v>22</v>
+      </c>
+      <c r="Q8">
+        <v>18</v>
+      </c>
+      <c r="R8">
+        <v>15</v>
+      </c>
+      <c r="S8">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
+        <v>gk_002</v>
+      </c>
+      <c r="B9" t="str">
+        <v>钱国门</v>
+      </c>
+      <c r="C9" t="str">
+        <v>GK</v>
+      </c>
+      <c r="D9">
+        <v>4</v>
+      </c>
+      <c r="E9">
+        <v>22</v>
+      </c>
+      <c r="F9">
+        <v>90</v>
+      </c>
+      <c r="G9">
+        <v>55</v>
+      </c>
+      <c r="H9">
+        <v>62</v>
+      </c>
+      <c r="I9" t="str">
+        <v>skill_save</v>
+      </c>
+      <c r="J9" t="str">
+        <v>skill_dragon</v>
+      </c>
+      <c r="K9" t="str">
+        <v>card_gk_002</v>
+      </c>
+      <c r="L9" t="str">
+        <v>铁门罗汉，扑救如有神助</v>
+      </c>
+      <c r="M9">
+        <v>22</v>
+      </c>
+      <c r="N9">
+        <v>35</v>
+      </c>
+      <c r="O9">
+        <v>12</v>
+      </c>
+      <c r="P9">
+        <v>35</v>
+      </c>
+      <c r="Q9">
+        <v>30</v>
+      </c>
+      <c r="R9">
+        <v>75</v>
+      </c>
+      <c r="S9">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>df_003</v>
+      </c>
+      <c r="B10" t="str">
+        <v>马铜墙</v>
+      </c>
+      <c r="C10" t="str">
+        <v>DEF</v>
+      </c>
+      <c r="D10">
+        <v>3</v>
+      </c>
+      <c r="E10">
+        <v>40</v>
+      </c>
+      <c r="F10">
+        <v>78</v>
+      </c>
+      <c r="G10">
+        <v>58</v>
+      </c>
+      <c r="H10">
+        <v>55</v>
+      </c>
+      <c r="I10" t="str">
+        <v>skill_iron_wall</v>
+      </c>
+      <c r="J10" t="str">
+        <v>skill_tiger</v>
+      </c>
+      <c r="K10" t="str">
+        <v>card_df_003</v>
+      </c>
+      <c r="L10" t="str">
+        <v>排山倒海掌，攻守兼备后卫</v>
+      </c>
+      <c r="M10">
+        <v>42</v>
+      </c>
+      <c r="N10">
+        <v>50</v>
+      </c>
+      <c r="O10">
+        <v>35</v>
+      </c>
+      <c r="P10">
+        <v>78</v>
+      </c>
+      <c r="Q10">
+        <v>72</v>
+      </c>
+      <c r="R10">
+        <v>75</v>
+      </c>
+      <c r="S10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>mf_003</v>
+      </c>
+      <c r="B11" t="str">
+        <v>杨旋风</v>
+      </c>
+      <c r="C11" t="str">
+        <v>MID</v>
+      </c>
+      <c r="D11">
+        <v>3</v>
+      </c>
+      <c r="E11">
+        <v>62</v>
+      </c>
+      <c r="F11">
+        <v>55</v>
+      </c>
+      <c r="G11">
+        <v>72</v>
+      </c>
+      <c r="H11">
+        <v>70</v>
+      </c>
+      <c r="I11" t="str">
+        <v>skill_shadow</v>
+      </c>
+      <c r="J11" t="str">
+        <v/>
+      </c>
+      <c r="K11" t="str">
+        <v>card_mf_003</v>
+      </c>
+      <c r="L11" t="str">
+        <v>醉拳少年，飘忽不定</v>
+      </c>
+      <c r="M11">
+        <v>72</v>
+      </c>
+      <c r="N11">
+        <v>65</v>
+      </c>
+      <c r="O11">
+        <v>58</v>
+      </c>
+      <c r="P11">
+        <v>55</v>
+      </c>
+      <c r="Q11">
+        <v>52</v>
+      </c>
+      <c r="R11">
+        <v>38</v>
+      </c>
+      <c r="S11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>mf_004</v>
+      </c>
+      <c r="B12" t="str">
+        <v>刘组织</v>
+      </c>
+      <c r="C12" t="str">
+        <v>MID</v>
+      </c>
+      <c r="D12">
+        <v>4</v>
+      </c>
+      <c r="E12">
+        <v>58</v>
+      </c>
+      <c r="F12">
+        <v>60</v>
+      </c>
+      <c r="G12">
+        <v>68</v>
+      </c>
+      <c r="H12">
+        <v>88</v>
+      </c>
+      <c r="I12" t="str">
+        <v>skill_through</v>
+      </c>
+      <c r="J12" t="str">
+        <v>skill_eagle</v>
+      </c>
+      <c r="K12" t="str">
+        <v>card_mf_004</v>
+      </c>
+      <c r="L12" t="str">
+        <v>八卦掌宗师，传球出神入化</v>
+      </c>
+      <c r="M12">
+        <v>62</v>
+      </c>
+      <c r="N12">
+        <v>88</v>
+      </c>
+      <c r="O12">
+        <v>52</v>
+      </c>
+      <c r="P12">
+        <v>58</v>
+      </c>
+      <c r="Q12">
+        <v>60</v>
+      </c>
+      <c r="R12">
+        <v>42</v>
+      </c>
+      <c r="S12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
         <v>fw_003</v>
       </c>
-      <c r="B9" t="str">
+      <c r="B13" t="str">
         <v>周重炮</v>
       </c>
-      <c r="C9" t="str">
+      <c r="C13" t="str">
         <v>FWD</v>
       </c>
-      <c r="D9">
+      <c r="D13">
+        <v>4</v>
+      </c>
+      <c r="E13">
+        <v>88</v>
+      </c>
+      <c r="F13">
+        <v>22</v>
+      </c>
+      <c r="G13">
+        <v>72</v>
+      </c>
+      <c r="H13">
+        <v>82</v>
+      </c>
+      <c r="I13" t="str">
+        <v>skill_shot</v>
+      </c>
+      <c r="J13" t="str">
+        <v>skill_thunder</v>
+      </c>
+      <c r="K13" t="str">
+        <v>card_fw_003</v>
+      </c>
+      <c r="L13" t="str">
+        <v>降龙十八脚，射门势大力沉</v>
+      </c>
+      <c r="M13">
+        <v>75</v>
+      </c>
+      <c r="N13">
+        <v>60</v>
+      </c>
+      <c r="O13">
+        <v>88</v>
+      </c>
+      <c r="P13">
+        <v>20</v>
+      </c>
+      <c r="Q13">
+        <v>18</v>
+      </c>
+      <c r="R13">
+        <v>15</v>
+      </c>
+      <c r="S13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>fw_004</v>
+      </c>
+      <c r="B14" t="str">
+        <v>吴闪电</v>
+      </c>
+      <c r="C14" t="str">
+        <v>FWD</v>
+      </c>
+      <c r="D14">
+        <v>4</v>
+      </c>
+      <c r="E14">
+        <v>82</v>
+      </c>
+      <c r="F14">
+        <v>28</v>
+      </c>
+      <c r="G14">
+        <v>92</v>
+      </c>
+      <c r="H14">
+        <v>78</v>
+      </c>
+      <c r="I14" t="str">
+        <v>skill_dribble</v>
+      </c>
+      <c r="J14" t="str">
+        <v>skill_shadow</v>
+      </c>
+      <c r="K14" t="str">
+        <v>card_fw_004</v>
+      </c>
+      <c r="L14" t="str">
+        <v>闪电连环腿，速度即正义</v>
+      </c>
+      <c r="M14">
+        <v>88</v>
+      </c>
+      <c r="N14">
+        <v>62</v>
+      </c>
+      <c r="O14">
+        <v>82</v>
+      </c>
+      <c r="P14">
+        <v>25</v>
+      </c>
+      <c r="Q14">
+        <v>22</v>
+      </c>
+      <c r="R14">
+        <v>16</v>
+      </c>
+      <c r="S14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>fw_005</v>
+      </c>
+      <c r="B15" t="str">
+        <v>郑武神</v>
+      </c>
+      <c r="C15" t="str">
+        <v>FWD</v>
+      </c>
+      <c r="D15">
         <v>5</v>
       </c>
-      <c r="E9">
+      <c r="E15">
         <v>95</v>
       </c>
-      <c r="F9">
+      <c r="F15">
+        <v>25</v>
+      </c>
+      <c r="G15">
+        <v>88</v>
+      </c>
+      <c r="H15">
+        <v>92</v>
+      </c>
+      <c r="I15" t="str">
+        <v>skill_thunder</v>
+      </c>
+      <c r="J15" t="str">
+        <v>skill_freekick</v>
+      </c>
+      <c r="K15" t="str">
+        <v>card_fw_005</v>
+      </c>
+      <c r="L15" t="str">
+        <v>功夫足球之王，无人能挡</v>
+      </c>
+      <c r="M15">
+        <v>90</v>
+      </c>
+      <c r="N15">
+        <v>72</v>
+      </c>
+      <c r="O15">
+        <v>95</v>
+      </c>
+      <c r="P15">
+        <v>22</v>
+      </c>
+      <c r="Q15">
         <v>20</v>
       </c>
-      <c r="G9">
+      <c r="R15">
+        <v>18</v>
+      </c>
+      <c r="S15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>ai_gk_01</v>
+      </c>
+      <c r="B16" t="str">
+        <v>何小门</v>
+      </c>
+      <c r="C16" t="str">
+        <v>GK</v>
+      </c>
+      <c r="D16">
+        <v>1</v>
+      </c>
+      <c r="E16">
+        <v>10</v>
+      </c>
+      <c r="F16">
+        <v>45</v>
+      </c>
+      <c r="G16">
+        <v>30</v>
+      </c>
+      <c r="H16">
+        <v>28</v>
+      </c>
+      <c r="I16" t="str">
+        <v>skill_save</v>
+      </c>
+      <c r="J16" t="str">
+        <v/>
+      </c>
+      <c r="K16" t="str">
+        <v>card_gk_001</v>
+      </c>
+      <c r="L16" t="str">
+        <v>菜鸟守门员，有待成长</v>
+      </c>
+      <c r="M16">
+        <v>10</v>
+      </c>
+      <c r="N16">
+        <v>15</v>
+      </c>
+      <c r="O16">
+        <v>5</v>
+      </c>
+      <c r="P16">
+        <v>15</v>
+      </c>
+      <c r="Q16">
+        <v>12</v>
+      </c>
+      <c r="R16">
+        <v>30</v>
+      </c>
+      <c r="S16">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>ai_df_01</v>
+      </c>
+      <c r="B17" t="str">
+        <v>胡矮墙</v>
+      </c>
+      <c r="C17" t="str">
+        <v>DEF</v>
+      </c>
+      <c r="D17">
+        <v>1</v>
+      </c>
+      <c r="E17">
+        <v>18</v>
+      </c>
+      <c r="F17">
+        <v>42</v>
+      </c>
+      <c r="G17">
+        <v>32</v>
+      </c>
+      <c r="H17">
+        <v>25</v>
+      </c>
+      <c r="I17" t="str">
+        <v>skill_tackle</v>
+      </c>
+      <c r="J17" t="str">
+        <v/>
+      </c>
+      <c r="K17" t="str">
+        <v>card_df_001</v>
+      </c>
+      <c r="L17" t="str">
+        <v>新手后卫，勉强能防</v>
+      </c>
+      <c r="M17">
+        <v>18</v>
+      </c>
+      <c r="N17">
+        <v>22</v>
+      </c>
+      <c r="O17">
+        <v>15</v>
+      </c>
+      <c r="P17">
+        <v>42</v>
+      </c>
+      <c r="Q17">
+        <v>38</v>
+      </c>
+      <c r="R17">
+        <v>35</v>
+      </c>
+      <c r="S17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>ai_mf_01</v>
+      </c>
+      <c r="B18" t="str">
+        <v>曹学徒</v>
+      </c>
+      <c r="C18" t="str">
+        <v>MID</v>
+      </c>
+      <c r="D18">
+        <v>1</v>
+      </c>
+      <c r="E18">
+        <v>28</v>
+      </c>
+      <c r="F18">
+        <v>25</v>
+      </c>
+      <c r="G18">
+        <v>35</v>
+      </c>
+      <c r="H18">
+        <v>32</v>
+      </c>
+      <c r="I18" t="str">
+        <v/>
+      </c>
+      <c r="J18" t="str">
+        <v/>
+      </c>
+      <c r="K18" t="str">
+        <v>card_mf_001</v>
+      </c>
+      <c r="L18" t="str">
+        <v>初入江湖的学徒</v>
+      </c>
+      <c r="M18">
+        <v>30</v>
+      </c>
+      <c r="N18">
+        <v>32</v>
+      </c>
+      <c r="O18">
+        <v>25</v>
+      </c>
+      <c r="P18">
+        <v>25</v>
+      </c>
+      <c r="Q18">
+        <v>22</v>
+      </c>
+      <c r="R18">
+        <v>18</v>
+      </c>
+      <c r="S18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>ai_mf_02</v>
+      </c>
+      <c r="B19" t="str">
+        <v>韩旋风</v>
+      </c>
+      <c r="C19" t="str">
+        <v>MID</v>
+      </c>
+      <c r="D19">
+        <v>1</v>
+      </c>
+      <c r="E19">
+        <v>30</v>
+      </c>
+      <c r="F19">
+        <v>22</v>
+      </c>
+      <c r="G19">
+        <v>40</v>
+      </c>
+      <c r="H19">
+        <v>35</v>
+      </c>
+      <c r="I19" t="str">
+        <v>skill_dribble</v>
+      </c>
+      <c r="J19" t="str">
+        <v/>
+      </c>
+      <c r="K19" t="str">
+        <v>card_mf_002</v>
+      </c>
+      <c r="L19" t="str">
+        <v>爱好旋转的少年</v>
+      </c>
+      <c r="M19">
+        <v>38</v>
+      </c>
+      <c r="N19">
+        <v>28</v>
+      </c>
+      <c r="O19">
+        <v>28</v>
+      </c>
+      <c r="P19">
+        <v>22</v>
+      </c>
+      <c r="Q19">
+        <v>20</v>
+      </c>
+      <c r="R19">
+        <v>15</v>
+      </c>
+      <c r="S19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>ai_fw_01</v>
+      </c>
+      <c r="B20" t="str">
+        <v>黄毛头</v>
+      </c>
+      <c r="C20" t="str">
+        <v>FWD</v>
+      </c>
+      <c r="D20">
+        <v>1</v>
+      </c>
+      <c r="E20">
+        <v>38</v>
+      </c>
+      <c r="F20">
+        <v>12</v>
+      </c>
+      <c r="G20">
+        <v>42</v>
+      </c>
+      <c r="H20">
+        <v>30</v>
+      </c>
+      <c r="I20" t="str">
+        <v>skill_shot</v>
+      </c>
+      <c r="J20" t="str">
+        <v/>
+      </c>
+      <c r="K20" t="str">
+        <v>card_fw_001</v>
+      </c>
+      <c r="L20" t="str">
+        <v>冲劲十足的愣头青</v>
+      </c>
+      <c r="M20">
+        <v>35</v>
+      </c>
+      <c r="N20">
+        <v>22</v>
+      </c>
+      <c r="O20">
+        <v>38</v>
+      </c>
+      <c r="P20">
+        <v>12</v>
+      </c>
+      <c r="Q20">
+        <v>10</v>
+      </c>
+      <c r="R20">
+        <v>8</v>
+      </c>
+      <c r="S20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>ai_df_02</v>
+      </c>
+      <c r="B21" t="str">
+        <v>许蛮力</v>
+      </c>
+      <c r="C21" t="str">
+        <v>DEF</v>
+      </c>
+      <c r="D21">
+        <v>2</v>
+      </c>
+      <c r="E21">
+        <v>28</v>
+      </c>
+      <c r="F21">
+        <v>58</v>
+      </c>
+      <c r="G21">
+        <v>42</v>
+      </c>
+      <c r="H21">
+        <v>35</v>
+      </c>
+      <c r="I21" t="str">
+        <v>skill_tackle</v>
+      </c>
+      <c r="J21" t="str">
+        <v/>
+      </c>
+      <c r="K21" t="str">
+        <v>card_df_002</v>
+      </c>
+      <c r="L21" t="str">
+        <v>力大无穷的蛮力后卫</v>
+      </c>
+      <c r="M21">
+        <v>28</v>
+      </c>
+      <c r="N21">
+        <v>32</v>
+      </c>
+      <c r="O21">
+        <v>22</v>
+      </c>
+      <c r="P21">
+        <v>58</v>
+      </c>
+      <c r="Q21">
+        <v>52</v>
+      </c>
+      <c r="R21">
+        <v>50</v>
+      </c>
+      <c r="S21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>ai_mf_03</v>
+      </c>
+      <c r="B22" t="str">
+        <v>秦快手</v>
+      </c>
+      <c r="C22" t="str">
+        <v>MID</v>
+      </c>
+      <c r="D22">
+        <v>2</v>
+      </c>
+      <c r="E22">
+        <v>42</v>
+      </c>
+      <c r="F22">
+        <v>38</v>
+      </c>
+      <c r="G22">
+        <v>55</v>
+      </c>
+      <c r="H22">
+        <v>48</v>
+      </c>
+      <c r="I22" t="str">
+        <v>skill_through</v>
+      </c>
+      <c r="J22" t="str">
+        <v/>
+      </c>
+      <c r="K22" t="str">
+        <v>card_mf_001</v>
+      </c>
+      <c r="L22" t="str">
+        <v>手脚麻利的中场球员</v>
+      </c>
+      <c r="M22">
+        <v>48</v>
+      </c>
+      <c r="N22">
+        <v>50</v>
+      </c>
+      <c r="O22">
+        <v>38</v>
+      </c>
+      <c r="P22">
+        <v>38</v>
+      </c>
+      <c r="Q22">
+        <v>35</v>
+      </c>
+      <c r="R22">
+        <v>25</v>
+      </c>
+      <c r="S22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>ai_fw_02</v>
+      </c>
+      <c r="B23" t="str">
+        <v>魏快刀</v>
+      </c>
+      <c r="C23" t="str">
+        <v>FWD</v>
+      </c>
+      <c r="D23">
+        <v>2</v>
+      </c>
+      <c r="E23">
+        <v>55</v>
+      </c>
+      <c r="F23">
+        <v>18</v>
+      </c>
+      <c r="G23">
+        <v>60</v>
+      </c>
+      <c r="H23">
+        <v>45</v>
+      </c>
+      <c r="I23" t="str">
+        <v>skill_shot</v>
+      </c>
+      <c r="J23" t="str">
+        <v/>
+      </c>
+      <c r="K23" t="str">
+        <v>card_fw_002</v>
+      </c>
+      <c r="L23" t="str">
+        <v>快刀斩乱麻的前锋</v>
+      </c>
+      <c r="M23">
+        <v>52</v>
+      </c>
+      <c r="N23">
+        <v>35</v>
+      </c>
+      <c r="O23">
+        <v>55</v>
+      </c>
+      <c r="P23">
+        <v>18</v>
+      </c>
+      <c r="Q23">
+        <v>15</v>
+      </c>
+      <c r="R23">
+        <v>12</v>
+      </c>
+      <c r="S23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>ai_gk_02</v>
+      </c>
+      <c r="B24" t="str">
+        <v>郭铁拳</v>
+      </c>
+      <c r="C24" t="str">
+        <v>GK</v>
+      </c>
+      <c r="D24">
+        <v>3</v>
+      </c>
+      <c r="E24">
+        <v>18</v>
+      </c>
+      <c r="F24">
+        <v>75</v>
+      </c>
+      <c r="G24">
+        <v>48</v>
+      </c>
+      <c r="H24">
+        <v>50</v>
+      </c>
+      <c r="I24" t="str">
+        <v>skill_save</v>
+      </c>
+      <c r="J24" t="str">
+        <v/>
+      </c>
+      <c r="K24" t="str">
+        <v>card_gk_001</v>
+      </c>
+      <c r="L24" t="str">
+        <v>铁拳门将，扑救稳健</v>
+      </c>
+      <c r="M24">
+        <v>18</v>
+      </c>
+      <c r="N24">
+        <v>28</v>
+      </c>
+      <c r="O24">
+        <v>10</v>
+      </c>
+      <c r="P24">
+        <v>28</v>
+      </c>
+      <c r="Q24">
+        <v>22</v>
+      </c>
+      <c r="R24">
+        <v>58</v>
+      </c>
+      <c r="S24">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>ai_df_03</v>
+      </c>
+      <c r="B25" t="str">
+        <v>蒋硬壳</v>
+      </c>
+      <c r="C25" t="str">
+        <v>DEF</v>
+      </c>
+      <c r="D25">
+        <v>3</v>
+      </c>
+      <c r="E25">
+        <v>35</v>
+      </c>
+      <c r="F25">
+        <v>75</v>
+      </c>
+      <c r="G25">
+        <v>52</v>
+      </c>
+      <c r="H25">
+        <v>48</v>
+      </c>
+      <c r="I25" t="str">
+        <v>skill_tackle</v>
+      </c>
+      <c r="J25" t="str">
+        <v>skill_iron_wall</v>
+      </c>
+      <c r="K25" t="str">
+        <v>card_df_001</v>
+      </c>
+      <c r="L25" t="str">
+        <v>硬如龟壳的铁血后卫</v>
+      </c>
+      <c r="M25">
+        <v>35</v>
+      </c>
+      <c r="N25">
+        <v>42</v>
+      </c>
+      <c r="O25">
+        <v>28</v>
+      </c>
+      <c r="P25">
+        <v>75</v>
+      </c>
+      <c r="Q25">
         <v>70</v>
       </c>
-      <c r="H9">
-        <v>88</v>
-      </c>
-      <c r="I9" t="str">
+      <c r="R25">
+        <v>72</v>
+      </c>
+      <c r="S25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>ai_mf_04</v>
+      </c>
+      <c r="B26" t="str">
+        <v>谢剑气</v>
+      </c>
+      <c r="C26" t="str">
+        <v>MID</v>
+      </c>
+      <c r="D26">
+        <v>3</v>
+      </c>
+      <c r="E26">
+        <v>58</v>
+      </c>
+      <c r="F26">
+        <v>55</v>
+      </c>
+      <c r="G26">
+        <v>65</v>
+      </c>
+      <c r="H26">
+        <v>72</v>
+      </c>
+      <c r="I26" t="str">
+        <v>skill_through</v>
+      </c>
+      <c r="J26" t="str">
+        <v>skill_eagle</v>
+      </c>
+      <c r="K26" t="str">
+        <v>card_mf_002</v>
+      </c>
+      <c r="L26" t="str">
+        <v>剑气纵横的中场指挥官</v>
+      </c>
+      <c r="M26">
+        <v>62</v>
+      </c>
+      <c r="N26">
+        <v>72</v>
+      </c>
+      <c r="O26">
+        <v>52</v>
+      </c>
+      <c r="P26">
+        <v>55</v>
+      </c>
+      <c r="Q26">
+        <v>50</v>
+      </c>
+      <c r="R26">
+        <v>38</v>
+      </c>
+      <c r="S26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>ai_fw_03</v>
+      </c>
+      <c r="B27" t="str">
+        <v>施烈火</v>
+      </c>
+      <c r="C27" t="str">
+        <v>FWD</v>
+      </c>
+      <c r="D27">
+        <v>3</v>
+      </c>
+      <c r="E27">
+        <v>72</v>
+      </c>
+      <c r="F27">
+        <v>22</v>
+      </c>
+      <c r="G27">
+        <v>70</v>
+      </c>
+      <c r="H27">
+        <v>65</v>
+      </c>
+      <c r="I27" t="str">
         <v>skill_shot</v>
       </c>
-      <c r="J9" t="str">
+      <c r="J27" t="str">
+        <v>skill_dribble</v>
+      </c>
+      <c r="K27" t="str">
+        <v>card_fw_001</v>
+      </c>
+      <c r="L27" t="str">
+        <v>烈火焚城的暴力前锋</v>
+      </c>
+      <c r="M27">
+        <v>68</v>
+      </c>
+      <c r="N27">
+        <v>50</v>
+      </c>
+      <c r="O27">
+        <v>72</v>
+      </c>
+      <c r="P27">
+        <v>20</v>
+      </c>
+      <c r="Q27">
+        <v>18</v>
+      </c>
+      <c r="R27">
+        <v>15</v>
+      </c>
+      <c r="S27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>ai_df_04</v>
+      </c>
+      <c r="B28" t="str">
+        <v>沈盾牌</v>
+      </c>
+      <c r="C28" t="str">
+        <v>DEF</v>
+      </c>
+      <c r="D28">
+        <v>4</v>
+      </c>
+      <c r="E28">
+        <v>42</v>
+      </c>
+      <c r="F28">
+        <v>85</v>
+      </c>
+      <c r="G28">
+        <v>58</v>
+      </c>
+      <c r="H28">
+        <v>55</v>
+      </c>
+      <c r="I28" t="str">
+        <v>skill_iron_wall</v>
+      </c>
+      <c r="J28" t="str">
+        <v>skill_tiger</v>
+      </c>
+      <c r="K28" t="str">
+        <v>card_df_002</v>
+      </c>
+      <c r="L28" t="str">
+        <v>无懈可击的盾牌后卫</v>
+      </c>
+      <c r="M28">
+        <v>42</v>
+      </c>
+      <c r="N28">
+        <v>48</v>
+      </c>
+      <c r="O28">
+        <v>35</v>
+      </c>
+      <c r="P28">
+        <v>85</v>
+      </c>
+      <c r="Q28">
+        <v>80</v>
+      </c>
+      <c r="R28">
+        <v>82</v>
+      </c>
+      <c r="S28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>ai_mf_05</v>
+      </c>
+      <c r="B29" t="str">
+        <v>邹无双</v>
+      </c>
+      <c r="C29" t="str">
+        <v>MID</v>
+      </c>
+      <c r="D29">
+        <v>4</v>
+      </c>
+      <c r="E29">
+        <v>68</v>
+      </c>
+      <c r="F29">
+        <v>62</v>
+      </c>
+      <c r="G29">
+        <v>75</v>
+      </c>
+      <c r="H29">
+        <v>85</v>
+      </c>
+      <c r="I29" t="str">
+        <v>skill_eagle</v>
+      </c>
+      <c r="J29" t="str">
+        <v>skill_shadow</v>
+      </c>
+      <c r="K29" t="str">
+        <v>card_mf_001</v>
+      </c>
+      <c r="L29" t="str">
+        <v>无双中场大师</v>
+      </c>
+      <c r="M29">
+        <v>72</v>
+      </c>
+      <c r="N29">
+        <v>85</v>
+      </c>
+      <c r="O29">
+        <v>62</v>
+      </c>
+      <c r="P29">
+        <v>62</v>
+      </c>
+      <c r="Q29">
+        <v>58</v>
+      </c>
+      <c r="R29">
+        <v>45</v>
+      </c>
+      <c r="S29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>ai_fw_04</v>
+      </c>
+      <c r="B30" t="str">
+        <v>方破军</v>
+      </c>
+      <c r="C30" t="str">
+        <v>FWD</v>
+      </c>
+      <c r="D30">
+        <v>4</v>
+      </c>
+      <c r="E30">
+        <v>85</v>
+      </c>
+      <c r="F30">
+        <v>25</v>
+      </c>
+      <c r="G30">
+        <v>82</v>
+      </c>
+      <c r="H30">
+        <v>80</v>
+      </c>
+      <c r="I30" t="str">
+        <v>skill_thunder</v>
+      </c>
+      <c r="J30" t="str">
+        <v>skill_dribble</v>
+      </c>
+      <c r="K30" t="str">
+        <v>card_fw_002</v>
+      </c>
+      <c r="L30" t="str">
+        <v>破军杀招的恐怖射手</v>
+      </c>
+      <c r="M30">
+        <v>82</v>
+      </c>
+      <c r="N30">
+        <v>60</v>
+      </c>
+      <c r="O30">
+        <v>85</v>
+      </c>
+      <c r="P30">
+        <v>22</v>
+      </c>
+      <c r="Q30">
+        <v>20</v>
+      </c>
+      <c r="R30">
+        <v>15</v>
+      </c>
+      <c r="S30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>ai_gk_03</v>
+      </c>
+      <c r="B31" t="str">
+        <v>段铁壁</v>
+      </c>
+      <c r="C31" t="str">
+        <v>GK</v>
+      </c>
+      <c r="D31">
+        <v>5</v>
+      </c>
+      <c r="E31">
+        <v>25</v>
+      </c>
+      <c r="F31">
+        <v>95</v>
+      </c>
+      <c r="G31">
+        <v>58</v>
+      </c>
+      <c r="H31">
+        <v>68</v>
+      </c>
+      <c r="I31" t="str">
+        <v>skill_save</v>
+      </c>
+      <c r="J31" t="str">
+        <v>skill_dragon</v>
+      </c>
+      <c r="K31" t="str">
+        <v>card_gk_001</v>
+      </c>
+      <c r="L31" t="str">
+        <v>绝世门神，固若金汤</v>
+      </c>
+      <c r="M31">
+        <v>25</v>
+      </c>
+      <c r="N31">
+        <v>38</v>
+      </c>
+      <c r="O31">
+        <v>15</v>
+      </c>
+      <c r="P31">
+        <v>38</v>
+      </c>
+      <c r="Q31">
+        <v>32</v>
+      </c>
+      <c r="R31">
+        <v>80</v>
+      </c>
+      <c r="S31">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>ai_df_05</v>
+      </c>
+      <c r="B32" t="str">
+        <v>褚金刚</v>
+      </c>
+      <c r="C32" t="str">
+        <v>DEF</v>
+      </c>
+      <c r="D32">
+        <v>5</v>
+      </c>
+      <c r="E32">
+        <v>48</v>
+      </c>
+      <c r="F32">
+        <v>95</v>
+      </c>
+      <c r="G32">
+        <v>62</v>
+      </c>
+      <c r="H32">
+        <v>65</v>
+      </c>
+      <c r="I32" t="str">
+        <v>skill_iron_wall</v>
+      </c>
+      <c r="J32" t="str">
+        <v>skill_tiger</v>
+      </c>
+      <c r="K32" t="str">
+        <v>card_df_001</v>
+      </c>
+      <c r="L32" t="str">
+        <v>金刚不坏之体</v>
+      </c>
+      <c r="M32">
+        <v>48</v>
+      </c>
+      <c r="N32">
+        <v>55</v>
+      </c>
+      <c r="O32">
+        <v>40</v>
+      </c>
+      <c r="P32">
+        <v>95</v>
+      </c>
+      <c r="Q32">
+        <v>90</v>
+      </c>
+      <c r="R32">
+        <v>92</v>
+      </c>
+      <c r="S32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>ai_fw_05</v>
+      </c>
+      <c r="B33" t="str">
+        <v>龙啸天</v>
+      </c>
+      <c r="C33" t="str">
+        <v>FWD</v>
+      </c>
+      <c r="D33">
+        <v>5</v>
+      </c>
+      <c r="E33">
+        <v>95</v>
+      </c>
+      <c r="F33">
+        <v>28</v>
+      </c>
+      <c r="G33">
+        <v>90</v>
+      </c>
+      <c r="H33">
+        <v>92</v>
+      </c>
+      <c r="I33" t="str">
+        <v>skill_thunder</v>
+      </c>
+      <c r="J33" t="str">
         <v>skill_freekick</v>
       </c>
-      <c r="K9" t="str">
-        <v>card_fw_003</v>
-      </c>
-      <c r="L9" t="str">
-        <v>传奇射手</v>
+      <c r="K33" t="str">
+        <v>card_fw_001</v>
+      </c>
+      <c r="L33" t="str">
+        <v>龙啸九天，天下无敌</v>
+      </c>
+      <c r="M33">
+        <v>92</v>
+      </c>
+      <c r="N33">
+        <v>70</v>
+      </c>
+      <c r="O33">
+        <v>95</v>
+      </c>
+      <c r="P33">
+        <v>25</v>
+      </c>
+      <c r="Q33">
+        <v>22</v>
+      </c>
+      <c r="R33">
+        <v>18</v>
+      </c>
+      <c r="S33">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L9"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:S33"/>
   </ignoredErrors>
 </worksheet>
 </file>